--- a/translation/review/000scriptAKYO_0020T.xlsx
+++ b/translation/review/000scriptAKYO_0020T.xlsx
@@ -25,7 +25,7 @@
     <t>Kyousuke-shi, if you don't calm Kiririn-shi's wrath...</t>
   </si>
   <si>
-    <t>Kyousuke-shi, si no apaciguas la ira de Kiririn-shi...</t>
+    <t>Kyousuke-shi, si no apaciguas la ira de＿Kiririn-shi...</t>
   </si>
   <si>
     <t>Kyousuke</t>
@@ -40,7 +40,7 @@
     <t>If that's the case, 'tis the occasion for a "Two-Shot Conversation"!</t>
   </si>
   <si>
-    <t>¡En ese caso, es el momento para una «Conversación a Dueto»!</t>
+    <t>¡En ese caso, es el momento para una＿«Conversación a Dueto»!</t>
   </si>
   <si>
     <t>A "Two-Shot Conversation"? What's that?</t>
@@ -52,13 +52,13 @@
     <t>Venturing towards an honest one on one conversation with Kiririn-shi!</t>
   </si>
   <si>
-    <t>¡Adentrándose hacia una conversación sincera de uno a uno con Kiririn-shi!</t>
+    <t>¡Adentrándose hacia una conversación sincera＿de uno a uno con Kiririn-shi!</t>
   </si>
   <si>
     <t>React accordingly to the other party's speech and "retort" at the appropriate time!</t>
   </si>
   <si>
-    <t>¡Reacciona según las palabras de la otra parte y «contraataca» en el momento oportuno!</t>
+    <t>¡Reacciona según las palabras de la otra parte y＿«contraataca» en el momento oportuno!</t>
   </si>
   <si>
     <t>I-I get it. I'll give it a try...</t>
@@ -70,7 +70,7 @@
     <t>Watch it, there's also times where you don't gotta "retort"!</t>
   </si>
   <si>
-    <t>¡Ojo, también hay momentos en los que no debes «contraatacar»!</t>
+    <t>¡Ojo, también hay momentos en los que no＿debes «contraatacar»!</t>
   </si>
   <si>
     <t>Kirino</t>
@@ -79,13 +79,13 @@
     <t>What are you mumbling about? You pervert! Just die already!</t>
   </si>
   <si>
-    <t>¿Qué estás murmurando? ¡Pervertido! ¡Solo muérete ya!</t>
+    <t>¿Qué estás murmurando? ¡Pervertido! ¡Solo＿muérete ya!</t>
   </si>
   <si>
     <t>C-Calm down, Kirino... This is just a misunderstanding.</t>
   </si>
   <si>
-    <t>C-Cálmate, Kirino... Esto es solo un malentendido.</t>
+    <t>C-Cálmate, Kirino... Esto es solo un＿malentendido.</t>
   </si>
   <si>
     <t>Shut up! Don't deny it!</t>
@@ -97,13 +97,13 @@
     <t>Although I tried to "retort" her, it looks like it didn't work at all.</t>
   </si>
   <si>
-    <t>Aunque intenté «contraatacarla», parece que no funcionó en absoluto.</t>
+    <t>Aunque intenté «contraatacarla», parece que no＿funcionó en absoluto.</t>
   </si>
   <si>
     <t>As expected of Kyousuke-shi! A splendid retort!</t>
   </si>
   <si>
-    <t>¡Como era de esperar de Kyousuke-shi! ¡Un espléndido contraataque!</t>
+    <t>¡Como era de esperar de Kyousuke-shi! ¡Un＿espléndido contraataque!</t>
   </si>
   <si>
     <t>Kiririn-shi's wrath softened a little bit!</t>
@@ -142,7 +142,7 @@
     <t>Kyousuke-shi, hang in there! "Retort", "retort"!</t>
   </si>
   <si>
-    <t>¡Kyousuke-shi, aguanta! ¡«Contraataca», «contraataca»!</t>
+    <t>¡Kyousuke-shi, aguanta! ¡«Contraataca»,＿«contraataca»!</t>
   </si>
   <si>
     <t>I know. Okay, this time, I'll definitely...</t>
@@ -196,7 +196,7 @@
     <t>It's true! We can switch positions if you don't believe me! Then you'll know I couldn't see them from here!</t>
   </si>
   <si>
-    <t>¡Es verdad! ¡Podemos cambiar de posición si no me crees! ¡Entonces sabrás que no podía verlas desde aquí!</t>
+    <t>¡Es verdad! ¡Podemos cambiar de posición si no＿me crees! ¡Entonces sabrás que no podía verlas＿desde aquí!</t>
   </si>
   <si>
     <t>You tried?</t>
@@ -226,13 +226,13 @@
     <t>Ohhh! Nice one, Kyousuke-shi! Looks like you fixed up the misunderstanding with Kiririn-shi!</t>
   </si>
   <si>
-    <t>¡Oooh! ¡Bien hecho, Kyousuke-shi! ¡Parece que arreglaste el malentendido con Kiririn-shi!</t>
+    <t>¡Oooh! ¡Bien hecho, Kyousuke-shi! ¡Parece que＿arreglaste el malentendido con Kiririn-shi!</t>
   </si>
   <si>
     <t>Eh? No, but I just got called "stupid"... Right?</t>
   </si>
   <si>
-    <t>¿Eh? No, pero me acaban de llamar «estúpido»... ¿Verdad?</t>
+    <t>¿Eh? No, pero me acaban de llamar＿«estúpido»... ¿Verdad?</t>
   </si>
   <si>
     <t>Did I really clear up the misunderstanding?</t>
@@ -283,7 +283,7 @@
     <t>Did you bring my friends over to your room while I was gone?</t>
   </si>
   <si>
-    <t>¿Trajiste a mis amigas a tu cuarto mientras no estaba?</t>
+    <t>¿Trajiste a mis amigas a tu cuarto mientras no＿estaba?</t>
   </si>
   <si>
     <t>I-I didn't...</t>
@@ -301,13 +301,13 @@
     <t>Then, why did those two spontaneously come into your room today?</t>
   </si>
   <si>
-    <t>Entonces, ¿por qué esas dos entraron espontáneamente a tu cuarto hoy?</t>
+    <t>Entonces, ¿por qué esas dos entraron＿espontáneamente a tu cuarto hoy?</t>
   </si>
   <si>
     <t>The black one said it too: "We've always been gathering in this room".</t>
   </si>
   <si>
-    <t>La de negro también lo dijo: «Siempre nos hemos estado reuniendo en este cuarto».</t>
+    <t>La de negro también lo dijo: «Siempre nos＿hemos estado reuniendo en este cuarto».</t>
   </si>
   <si>
     <t>...What does that mean? Explain yourself.</t>
@@ -325,7 +325,7 @@
     <t>N-No, not by any means! Kiririn-shi! Heed my words!</t>
   </si>
   <si>
-    <t>¡N-No, en absoluto! ¡Kiririn-shi! ¡Escucha mis palabras!</t>
+    <t>¡N-No, en absoluto! ¡Kiririn-shi! ¡Escucha mis＿palabras!</t>
   </si>
   <si>
     <t>When Kiririn-shi took her leave, Kyousuke-shi...</t>
@@ -343,7 +343,7 @@
     <t>For that reason, Kuroneko-shi and I decided to raise this desolate fellow's spirits by arriving to play!</t>
   </si>
   <si>
-    <t>¡Por esa razón, Kuroneko-shi y yo decidimos levantar el ánimo de este desolado individuo viniendo a jugar!</t>
+    <t>¡Por esa razón, Kuroneko-shi y yo decidimos＿levantar el ánimo de este desolado individuo＿viniendo a jugar!</t>
   </si>
   <si>
     <t>Do you understand?</t>
@@ -382,7 +382,7 @@
     <t>Saori and Kuroneko were worried that I'd be lonely without you around.</t>
   </si>
   <si>
-    <t>Saori y Kuroneko se preocuparon de que estuviera solo sin ti.</t>
+    <t>Saori y Kuroneko se preocuparon de que＿estuviera solo sin ti.</t>
   </si>
   <si>
     <t>That's why they came to play so often.</t>
